--- a/data/gravel/Fara G4 2025.xlsx
+++ b/data/gravel/Fara G4 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{323797C7-71B2-DB43-8B81-84E643D6CC29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F72AD6A7-CDE5-3A4A-86F0-B3C867DE18B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27040" yWindow="-12500" windowWidth="24880" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -392,12 +392,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -753,19 +752,19 @@
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>101</v>
       </c>
     </row>
@@ -1141,13 +1140,13 @@
         <v>57</v>
       </c>
       <c r="D30" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E30" s="1">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F30" s="1">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:6">

--- a/data/gravel/Fara G4 2025.xlsx
+++ b/data/gravel/Fara G4 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F72AD6A7-CDE5-3A4A-86F0-B3C867DE18B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA3A1BA4-8EF8-8343-9909-3F0A854AEDF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="106">
   <si>
     <t>brand</t>
   </si>
@@ -348,6 +348,9 @@
   </si>
   <si>
     <t>threaded</t>
+  </si>
+  <si>
+    <t>https://framerusercontent.com/images/glqbKt37EAhNbiTiCkdvsxiog.png?scale-down-to=1024</t>
   </si>
 </sst>
 </file>
@@ -740,6 +743,11 @@
         <v>102</v>
       </c>
     </row>
+    <row r="6" spans="1:6">
+      <c r="B6" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
     <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
         <v>6</v>

--- a/data/gravel/Fara G4 2025.xlsx
+++ b/data/gravel/Fara G4 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA3A1BA4-8EF8-8343-9909-3F0A854AEDF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759A4732-07A1-8D4F-952F-5D2995AF9F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8020" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="108">
   <si>
     <t>brand</t>
   </si>
@@ -351,6 +351,12 @@
   </si>
   <si>
     <t>https://framerusercontent.com/images/glqbKt37EAhNbiTiCkdvsxiog.png?scale-down-to=1024</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Oslo, Norway</t>
   </si>
 </sst>
 </file>
@@ -696,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1472,6 +1478,14 @@
         <v>72</v>
       </c>
     </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Fara G4 2025.xlsx
+++ b/data/gravel/Fara G4 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759A4732-07A1-8D4F-952F-5D2995AF9F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05D1ED71-FB5B-EE4B-B1DF-0D6173DCBD83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8020" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="114">
   <si>
     <t>brand</t>
   </si>
@@ -357,6 +357,24 @@
   </si>
   <si>
     <t>Oslo, Norway</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -702,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1327,162 +1345,192 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>50</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B51" s="1">
-        <v>27.2</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>43</v>
+        <v>111</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>53</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>54</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B55" s="1">
-        <v>160</v>
+        <v>49</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B56" s="1">
-        <v>160</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
+      </c>
+      <c r="B57" s="1">
+        <v>27.2</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>37</v>
+        <v>55</v>
+      </c>
+      <c r="B61" s="1">
+        <v>160</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B62" s="1">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B65" s="1">
-        <v>3</v>
+        <v>59</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
+      </c>
+      <c r="B68" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="1" t="s">
-        <v>71</v>
+        <v>65</v>
+      </c>
+      <c r="B71" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="1" t="s">
-        <v>72</v>
+        <v>66</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B79" s="1" t="s">
         <v>107</v>
       </c>
     </row>
